--- a/pdf2img/hasil_ekstraksi/table_8/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_8/tabel_1.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,640 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>POSPOS</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>11.00.23</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>11.00:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RASO KINIRJA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kewa iban Peryedhaan hota Mirirur ((pyn)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'0.10%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1050%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Atot grodaf berrataiah dan atot "cn prodtot bo ledhadap lota atel produtl!</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gan total atot mon proruo!!</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>308%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Aset prod.all ber'rataiah torhadap lotal aset prod.tl!</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2M%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cadangan Keragan Perur.nar Nla iCxpN atet teuergan lerhadap atet proo.t!</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'02%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>专</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nid. groas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3674</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>主.昌</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>No not</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2 89%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>，</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ceur On Act(MOA)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C.Og</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>养</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rotrn on I guty (ROf)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>023%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Net intertat Margin (Nn)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>281%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(haya Operational toruadap Pendapalan Oper atuora (DOiO)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19.594</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>99515</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Coat to ncorme Rato (CIR)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9' 51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Loan lo Oepout Rabo (.DR)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>M401%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Noet Satip I unding Katio (NSi M)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0 NsiR seca'a ndrd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>147.62%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>145.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6NS+H seca'a Koroida</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nlan Iagarry Comrago Mato n Cu)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0 LcR tooaa ndmoy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>139.196</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>149.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>I Ct sotara Konsohdasi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nat I overage Rato (1 R)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2LR socra Mvcu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/3%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>9.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>（ua其rla</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KIPATUIAN (COWPLIANCD)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pertor ase Pelangparar pnn(</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Piak fertuail!</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>000%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>+Pihat Ticat "erua!</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0 00%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6Pertortate Peampalar Hatnk</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Piae Tart.t</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0 00%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>+ Ppat Tcat "erual</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0 00%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cro Wajb Mrurum (Gnh)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>a Gw yara rapiah</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>: Hartan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>000%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Raa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>6.064</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>6.95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>b Gwu vaca ating</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>435%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>016%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf2img/hasil_ekstraksi/table_8/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_8/tabel_1.xlsx
@@ -1042,10 +1042,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
@@ -1054,304 +1054,302 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>NO.</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>LAPORAN RASIO KEUANGAN Per 31 Desember 2025 dan 2024</t>
+          <t>POS-POS RASIO KINERJA</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 2</t>
+          <t>31-Des-25</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 3</t>
+          <t>( dalam jutaan rupiah ) 31-Des-24</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>NO.</t>
-        </is>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>POS-POS</t>
+          <t>Kewajiban Penyediaan Modal Minimum (KPMM)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>31-Des-25</t>
+          <t>10.10%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>( dalam jutaan rupiah ) 31-Des-24</t>
+          <t>10.50%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>RASIO KINERJA</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+          <t>Aset produktif bermasalah dan aset non produktif bermasalah terhadap total aset produktif dan total aset non produktif</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>3.08%</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Kewajiban Penyediaan Modal Minimum (KPMM)</t>
+          <t>Aset produktif bermasalah terhadap total aset produktif.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>10.10%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>10.50%</t>
+          <t>2,90%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Aset produktif bermasalah dan aset non produktif bermasalah terhadap total aset produktif dan total aset non produktif</t>
+          <t>Cadangan Kerugian Penurunan Nilai (CKPN) aset keuangan terhadap aset produktif</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Aset produktif bermasalah terhadap total aset produktif.</t>
+          <t>NPL gross</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2,90%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Cadangan Kerugian Penurunan Nilai (CKPN) aset keuangan terhadap aset produktif</t>
+          <t>NPL net</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>NPL gross</t>
+          <t>Return on Asset (ROA)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>NPL net</t>
+          <t>Return on Equity (ROE)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Return on Asset (ROA)</t>
+          <t>Net Interest Margin (NIM)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>2,10%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Return on Equity (ROE)</t>
+          <t>Biaya Operasional terhadap Pendapatan Operasional (BOPO)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>99.59%</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>99.51%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Net Interest Margin (NIM)</t>
+          <t>Cost to Income Ratio (CIR)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>86.81%</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2,10%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Biaya Operasional terhadap Pendapatan Operasional (BOPO)</t>
+          <t>Loan to Deposit Ratio (LDR)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>99.59%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>99.51%</t>
+          <t>84.01%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cost to Income Ratio (CIR)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>86.81%</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>91,53%</t>
-        </is>
-      </c>
+          <t>Net Stable Funding Ratio (NSFR)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="A15" s="3" t="inlineStr"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Loan to Deposit Ratio (LDR)</t>
+          <t>a. NSFR secara Individu b. NSFR secara Konsolidasi</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>147,62%</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>84.01%</t>
+          <t>145,19%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio (NSFR)</t>
+          <t>Nilai Liquidity Coverage Ratio (LCR)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
@@ -1361,27 +1359,27 @@
       <c r="A17" s="3" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>a. NSFR secara Individu b. NSFR secara Konsolidasi</t>
+          <t>a. LCR secara Individu b. LCR secara Konsolidasi</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>147,62%</t>
+          <t>139,19%</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>145,19%</t>
+          <t>149,69%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nilai Liquidity Coverage Ratio (LCR)</t>
+          <t>Nilai Leverage Ratio (LR)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
@@ -1391,27 +1389,25 @@
       <c r="A19" s="3" t="inlineStr"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>a. LCR secara Individu b. LCR secara Konsolidasi</t>
+          <t>a. LR secara Individu</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>139,19%</t>
+          <t>8.73%</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>149,69%</t>
+          <t>9,30%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="A20" s="3" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Nilai Leverage Ratio (LR)</t>
+          <t>b. LR secara Konsolidasi.</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
@@ -1421,25 +1417,19 @@
       <c r="A21" s="3" t="inlineStr"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>a. LR secara Individu</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>8.73%</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>9,30%</t>
-        </is>
-      </c>
+          <t>KEPATUHAN (COMPLIANCE)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>b. LR secara Konsolidasi.</t>
+          <t>a. Persentase Pelanggaran BMPK</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
@@ -1449,29 +1439,43 @@
       <c r="A23" s="3" t="inlineStr"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>KEPATUHAN (COMPLIANCE)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
+          <t>i. Pihak Terkait</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>0,00%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A24" s="3" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>a. Persentase Pelanggaran BMPK</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
+          <t>ii. Pihak Tidak Terkait</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>0,00%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>i. Pihak Terkait</t>
+          <t>b. Persentase Pelampauan BMPK i. Pihak Terkaite</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1499,63 +1503,63 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0,00%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
+      <c r="A27" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>b. Persentase Pelampauan BMPK i. Pihak Terkaite</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>0,00%</t>
-        </is>
-      </c>
+          <t>Giro Wajib Minimum (GWM)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ii. Pihak Tidak Terkait</t>
+          <t>a.GwM utama rupiah</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
+          <t>6.66%</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>. Harian</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Giro Wajib Minimum (GWM)</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>a.GwM utama rupiah</t>
+          <t>. Rata-rata</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1570,56 +1574,20 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr"/>
+      <c r="A31" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>. Harian</t>
+          <t>b. GWM valuta asing Posisi Devisa Neto (PDN) secara keseluruhan</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>4.35% 0.16%</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>. Rata-rata</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>6.66%</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>b. GWM valuta asing Posisi Devisa Neto (PDN) secara keseluruhan</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>4.35% 0.16%</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>4,30% 0.17%</t>
         </is>
